--- a/artfynd/A 53129-2025 artfynd.xlsx
+++ b/artfynd/A 53129-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,111 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129762076</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 53129, Segersgärde, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>577770</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6407008</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53129-2025 artfynd.xlsx
+++ b/artfynd/A 53129-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129762076</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53129-2025 artfynd.xlsx
+++ b/artfynd/A 53129-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129762076</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53129-2025 artfynd.xlsx
+++ b/artfynd/A 53129-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129762076</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53129-2025 artfynd.xlsx
+++ b/artfynd/A 53129-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74302187</v>
+        <v>129762076</v>
       </c>
       <c r="B2" t="n">
-        <v>98647</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Segersgärde 700 m SO, Sm</t>
+          <t>A 53129, Segersgärde, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577798</v>
+        <v>577770</v>
       </c>
       <c r="R2" t="n">
-        <v>6406959</v>
+        <v>6407008</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1982-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7G1f 3249. SOM: Epipactis helleborine. LEG: Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,80 +765,63 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129762076</v>
+        <v>74302187</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 53129, Segersgärde, Sm</t>
+          <t>Segersgärde 700 m SO, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577770</v>
+        <v>577798</v>
       </c>
       <c r="R3" t="n">
-        <v>6407008</v>
+        <v>6406959</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +845,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>1982-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G1f 3249. SOM: Epipactis helleborine. LEG: Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,18 +867,27 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
